--- a/college-posters/data/朋友圈文案.xlsx
+++ b/college-posters/data/朋友圈文案.xlsx
@@ -7950,7 +7950,7 @@
       <c r="K15" s="2" t="inlineStr">
         <is>
           <t>🎓 每天认识一所大学｜北京理工大学
-🏛️ 坐落北京，985 · 211 · 双一流高校，中国共产党创办的第一所理工科大学
+🏛️ 坐落北京，985 · 211 · 双一流高校，从延安窑洞走出的理工名校
 ⚙️ 兵器科学与技术学科评估A+，车辆工程值得重点了解
 📖 校训：德以明理，学以精工
 🌱 目标定得高一点，行动落得细一点，每一天都算数</t>
